--- a/data/mapas/Mapa_de_Carrera_Geografia.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Geografia.xlsx
@@ -555,13 +555,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B52, "SI")</f>
+        <f>COUNTIF(B6:B41, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C52, "SI")</f>
+        <f>COUNTIF(C6:C41, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F52, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F41, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Introducción a la Geografía</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B52, "SI")/41</f>
+        <f>COUNTIF(B6:B41, "SI")/32</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Cartografía y Sistemas de Información Geográfica (SIG)</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C52, "SI")/41</f>
+        <f>COUNTIF(C6:C41, "SI")/32</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Introducción a la Disciplina</t>
+          <t>Geografía Física I (Geomorfología y Geología)</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente I</t>
+          <t>Geografía Humana y Social I</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -831,10 +831,37 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Pedagogía</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E10" s="10">
+        <f>IF(B10="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F10" s="10">
+        <f>IF(C10="SI", "APROBADO", IF(B10="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
+        <f>IF(C10="SI", "🟢 Aprobada", IF(B10="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
@@ -845,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -860,7 +887,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E11" s="10">
@@ -884,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Sociología de la Educación</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -899,7 +926,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E12" s="10">
@@ -921,37 +948,10 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Sujetos de la Educación</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E13" s="10">
-        <f>IF(B13="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F13" s="10">
-        <f>IF(C13="SI", "APROBADO", IF(B13="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G13" s="11">
-        <f>IF(C13="SI", "🟢 Aprobada", IF(B13="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente II</t>
+          <t>Geografía Física II (Climatología, Hidrología y Biogeografía)</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -999,10 +999,37 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Geografía Económica y Urbana</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E15" s="10">
+        <f>IF(B15="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F15" s="10">
+        <f>IF(C15="SI", "APROBADO", IF(B15="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G15" s="11">
+        <f>IF(C15="SI", "🟢 Aprobada", IF(B15="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -1013,7 +1040,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Geografía de América Latina</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1028,7 +1055,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E16" s="10">
@@ -1047,7 +1074,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Residencia I</t>
+          <t>Geografía Rural y de la Población</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1062,7 +1089,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E17" s="10">
@@ -1081,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Espacio de Definición Institucional</t>
+          <t>Didáctica General</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1096,7 +1123,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E18" s="10">
@@ -1115,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente III</t>
+          <t>Psicología Educacional</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1130,7 +1157,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E19" s="10">
@@ -1146,17 +1173,44 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Sujetos de la Educación</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E20" s="10">
+        <f>IF(B20="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F20" s="10">
+        <f>IF(C20="SI", "APROBADO", IF(B20="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G20" s="11">
+        <f>IF(C20="SI", "🟢 Aprobada", IF(B20="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Residencia II / Taller de Cierre</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1171,7 +1225,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E21" s="10">
@@ -1187,44 +1241,17 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Ética y Trabajo Docente</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E22" s="10">
-        <f>IF(B22="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F22" s="10">
-        <f>IF(C22="SI", "APROBADO", IF(B22="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G22" s="11">
-        <f>IF(C22="SI", "🟢 Aprobada", IF(B22="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Investigación Educativa</t>
+          <t>Geografía de la República Argentina I (Bases Físicas y Ambientales)</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1239,7 +1266,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E23" s="10">
@@ -1258,7 +1285,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente IV</t>
+          <t>Geografía de la República Argentina II (Socioeconómica y Regional)</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1273,7 +1300,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E24" s="10">
@@ -1289,17 +1316,44 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>📌 5° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Geopolítica y Geografía Política</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E25" s="10">
+        <f>IF(B25="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F25" s="10">
+        <f>IF(C25="SI", "APROBADO", IF(B25="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G25" s="11">
+        <f>IF(C25="SI", "🟢 Aprobada", IF(B25="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Especialización Superior I</t>
+          <t>Didáctica de la Geografía I</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1314,7 +1368,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1333,7 +1387,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Taller de Investigación Aplicada</t>
+          <t>Historia Social de la Educación</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1348,7 +1402,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E27" s="10">
@@ -1367,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de Nivel Superior</t>
+          <t>Derechos Humanos, Sociedad y Estado</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1382,7 +1436,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E28" s="10">
@@ -1401,7 +1455,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Nivel Superior I</t>
+          <t>Construcción de la Práctica Docente I</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1416,7 +1470,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E29" s="10">
@@ -1435,14 +1489,14 @@
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>📌 6° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
+          <t>📌 4° AÑO</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Especialización Superior II</t>
+          <t>Geografía Mundial Contemporánea (Problemas Globales)</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1457,7 +1511,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E31" s="10">
@@ -1476,7 +1530,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Tesis / Trabajo Final de Licenciatura</t>
+          <t>Planificación Territorial y Problemáticas Ambientales</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1491,7 +1545,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1510,7 +1564,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Nivel Superior II</t>
+          <t>Epistemología e Historia del Pensamiento Geográfico</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1525,7 +1579,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1544,7 +1598,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Acreditación de Residencia Superior</t>
+          <t>Didáctica de la Geografía II</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1559,7 +1613,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1575,17 +1629,44 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>📌 GENERAL / OPTATIVAS</t>
-        </is>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Educación Sexual Integral (ESI)</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E35" s="10">
+        <f>IF(B35="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F35" s="10">
+        <f>IF(C35="SI", "APROBADO", IF(B35="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G35" s="11">
+        <f>IF(C35="SI", "🟢 Aprobada", IF(B35="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Antropologia</t>
+          <t>Ética y Trabajo Docente</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1600,7 +1681,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E36" s="10">
@@ -1619,7 +1700,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Derechos Humanos SOCIEDAD Y ESTADO</t>
+          <t>Residencia y Construcción de la Práctica Docente II</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1634,7 +1715,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E37" s="10">
@@ -1650,44 +1731,17 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>Ecologia y Biogeografia</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E38" s="10">
-        <f>IF(B38="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F38" s="10">
-        <f>IF(C38="SI", "APROBADO", IF(B38="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G38" s="11">
-        <f>IF(C38="SI", "🟢 Aprobada", IF(B38="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Economía Y TERRITORIOS</t>
+          <t>Seminario de Geografía Urbana y Metropolización</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -1702,7 +1756,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E39" s="10">
@@ -1721,7 +1775,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Educación Sexual Integral</t>
+          <t>Seminario de Recursos Naturales y Desarrollo Sustentable</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1736,7 +1790,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E40" s="10">
@@ -1755,7 +1809,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>ENS. DE LA Geografía. I Y CONST. Práctica DOCENTE</t>
+          <t>Taller de Investigación Geográfica</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1770,7 +1824,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E41" s="10">
@@ -1786,402 +1840,26 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>ENSEÑANZA Geografía II y Residencia</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E42" s="10">
-        <f>IF(B42="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F42" s="10">
-        <f>IF(C42="SI", "APROBADO", IF(B42="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G42" s="11">
-        <f>IF(C42="SI", "🟢 Aprobada", IF(B42="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>Filosofía</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E43" s="10">
-        <f>IF(B43="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F43" s="10">
-        <f>IF(C43="SI", "APROBADO", IF(B43="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G43" s="11">
-        <f>IF(C43="SI", "🟢 Aprobada", IF(B43="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>Geografía DE LA REPUBLICA ARGENTINA III</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E44" s="10">
-        <f>IF(B44="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F44" s="10">
-        <f>IF(C44="SI", "APROBADO", IF(B44="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G44" s="11">
-        <f>IF(C44="SI", "🟢 Aprobada", IF(B44="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>Geografía ECONOMICA MUNDIAL</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E45" s="10">
-        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F45" s="10">
-        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G45" s="11">
-        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>Historia Mundial</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E46" s="10">
-        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F46" s="10">
-        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G46" s="11">
-        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>Informacion Geografica I</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E47" s="10">
-        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F47" s="10">
-        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G47" s="11">
-        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>Posicionamiento Espacial y Geomatico</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E48" s="10">
-        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F48" s="10">
-        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G48" s="11">
-        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>Territorios I: America Latina y Anglo</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E49" s="10">
-        <f>IF(B49="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F49" s="10">
-        <f>IF(C49="SI", "APROBADO", IF(B49="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G49" s="11">
-        <f>IF(C49="SI", "🟢 Aprobada", IF(B49="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>Territorios I: America Latina y Anglosaj</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E50" s="10">
-        <f>IF(B50="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F50" s="10">
-        <f>IF(C50="SI", "APROBADO", IF(B50="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G50" s="11">
-        <f>IF(C50="SI", "🟢 Aprobada", IF(B50="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>Territorios Ii: Europa</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E51" s="10">
-        <f>IF(B51="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F51" s="10">
-        <f>IF(C51="SI", "APROBADO", IF(B51="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G51" s="11">
-        <f>IF(C51="SI", "🟢 Aprobada", IF(B51="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>Teledetección Geográfica</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E52" s="10">
-        <f>IF(B52="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F52" s="10">
-        <f>IF(C52="SI", "APROBADO", IF(B52="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G52" s="11">
-        <f>IF(C52="SI", "🟢 Aprobada", IF(B52="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="I14:J14"/>
+  <mergeCells count="15">
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A22:G22"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B11 B12 B13 B14 B16 B17 B18 B19 B21 B22 B23 B24 B26 B27 B28 B29 B31 B32 B33 B34 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45 B46 B47 B48 B49 B50 B51 B52 C6 C7 C8 C9 C11 C12 C13 C14 C16 C17 C18 C19 C21 C22 C23 C24 C26 C27 C28 C29 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 C52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B23 B24 B25 B26 B27 B28 B29 B31 B32 B33 B34 B35 B36 B37 B39 B40 B41 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C23 C24 C25 C26 C27 C28 C29 C31 C32 C33 C34 C35 C36 C37 C39 C40 C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/mapas/Mapa_de_Carrera_Geografia.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Geografia.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B41, "SI")</f>
+        <f>COUNTIF(B6:B51, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C41, "SI")</f>
+        <f>COUNTIF(C6:C51, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F41, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F51, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Introducción a la Geografía</t>
+          <t>Ciencias de la tierra 1: Geologia y paleontologia</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B41, "SI")/32</f>
+        <f>COUNTIF(B6:B51, "SI")/42</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Cartografía y Sistemas de Información Geográfica (SIG)</t>
+          <t>Información Geográfica 1</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C41, "SI")/32</f>
+        <f>COUNTIF(C6:C51, "SI")/42</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Geografía Física I (Geomorfología y Geología)</t>
+          <t>Dinamica de los procesos climaticos</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Geografía Humana y Social I</t>
+          <t>Introdución a la geografía</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Economía y territorios</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo I</t>
+          <t>Pedagogía</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -948,10 +948,37 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Psicología educacional</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E13" s="10">
+        <f>IF(B13="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F13" s="10">
+        <f>IF(C13="SI", "APROBADO", IF(B13="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G13" s="11">
+        <f>IF(C13="SI", "🟢 Aprobada", IF(B13="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -962,7 +989,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Geografía Física II (Climatología, Hidrología y Biogeografía)</t>
+          <t>Psicología del sujeto del nviel</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -977,7 +1004,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E14" s="10">
@@ -1001,7 +1028,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Geografía Económica y Urbana</t>
+          <t>Historia mundial</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1016,7 +1043,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E15" s="10">
@@ -1040,7 +1067,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Geografía de América Latina</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1055,7 +1082,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E16" s="10">
@@ -1071,44 +1098,17 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Geografía Rural y de la Población</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E17" s="10">
-        <f>IF(B17="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F17" s="10">
-        <f>IF(C17="SI", "APROBADO", IF(B17="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G17" s="11">
-        <f>IF(C17="SI", "🟢 Aprobada", IF(B17="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Posicionamiento espacial y geomatico</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1142,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Geografía Política</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1176,7 +1176,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Sujetos de la Educación</t>
+          <t>Ciencias de la tierra 2</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo II</t>
+          <t>Ecología y biogeografía</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1241,17 +1241,44 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Geografía Económica Mundial</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E22" s="10">
+        <f>IF(B22="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F22" s="10">
+        <f>IF(C22="SI", "APROBADO", IF(B22="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G22" s="11">
+        <f>IF(C22="SI", "🟢 Aprobada", IF(B22="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Geografía de la República Argentina I (Bases Físicas y Ambientales)</t>
+          <t>Territorios 1: America latina y anglosajona</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1266,7 +1293,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E23" s="10">
@@ -1285,7 +1312,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Geografía de la República Argentina II (Socioeconómica y Regional)</t>
+          <t>Didáctica general</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1300,7 +1327,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E24" s="10">
@@ -1319,7 +1346,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Geopolítica y Geografía Política</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -1334,7 +1361,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E25" s="10">
@@ -1353,7 +1380,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de la Geografía I</t>
+          <t>Historia social latinoamericana</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1368,7 +1395,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1384,44 +1411,17 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Historia Social de la Educación</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>3° Año</t>
-        </is>
-      </c>
-      <c r="E27" s="10">
-        <f>IF(B27="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F27" s="10">
-        <f>IF(C27="SI", "APROBADO", IF(B27="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G27" s="11">
-        <f>IF(C27="SI", "🟢 Aprobada", IF(B27="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Derechos Humanos, Sociedad y Estado</t>
+          <t>Información geográfica 2</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Construcción de la Práctica Docente I</t>
+          <t>Territorios 2: Europa</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1486,17 +1486,44 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Geografia de la Argentina 1</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E30" s="10">
+        <f>IF(B30="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F30" s="10">
+        <f>IF(C30="SI", "APROBADO", IF(B30="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G30" s="11">
+        <f>IF(C30="SI", "🟢 Aprobada", IF(B30="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Geografía Mundial Contemporánea (Problemas Globales)</t>
+          <t>Geografia de la Argentina 2</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E31" s="10">
@@ -1530,7 +1557,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Planificación Territorial y Problemáticas Ambientales</t>
+          <t>Construcción de la práctica docente y enseñanza de la geografía 1</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1545,7 +1572,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1564,7 +1591,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Epistemología e Historia del Pensamiento Geográfico</t>
+          <t>Historia de la educación Argentina</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1579,7 +1606,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1598,7 +1625,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de la Geografía II</t>
+          <t>Lectura, Escritura y Oralidad II (LEO 2)</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1613,7 +1640,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1632,7 +1659,7 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Educación Sexual Integral (ESI)</t>
+          <t>Filosofía</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -1647,7 +1674,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E35" s="10">
@@ -1666,7 +1693,7 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Ética y Trabajo Docente</t>
+          <t>DDHH, sociedad y estado</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1681,7 +1708,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E36" s="10">
@@ -1697,51 +1724,51 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>Residencia y Construcción de la Práctica Docente II</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Epistemología e historia de la geografía</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>4° Año</t>
         </is>
       </c>
-      <c r="E37" s="10">
-        <f>IF(B37="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F37" s="10">
-        <f>IF(C37="SI", "APROBADO", IF(B37="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G37" s="11">
-        <f>IF(C37="SI", "🟢 Aprobada", IF(B37="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
-        </is>
+      <c r="E38" s="10">
+        <f>IF(B38="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F38" s="10">
+        <f>IF(C38="SI", "APROBADO", IF(B38="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G38" s="11">
+        <f>IF(C38="SI", "🟢 Aprobada", IF(B38="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Geografía Urbana y Metropolización</t>
+          <t>Geografía de la Republica Argentina 3</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -1756,7 +1783,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E39" s="10">
@@ -1775,7 +1802,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Recursos Naturales y Desarrollo Sustentable</t>
+          <t>Geografía social</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1790,7 +1817,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E40" s="10">
@@ -1809,7 +1836,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Taller de Investigación Geográfica</t>
+          <t>Teledetección geográfica</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1824,7 +1851,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E41" s="10">
@@ -1840,26 +1867,339 @@
         <v/>
       </c>
     </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Problemáticas socioambientales</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E42" s="10">
+        <f>IF(B42="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F42" s="10">
+        <f>IF(C42="SI", "APROBADO", IF(B42="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G42" s="11">
+        <f>IF(C42="SI", "🟢 Aprobada", IF(B42="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Territorios 3: Asia</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E44" s="10">
+        <f>IF(B44="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F44" s="10">
+        <f>IF(C44="SI", "APROBADO", IF(B44="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G44" s="11">
+        <f>IF(C44="SI", "🟢 Aprobada", IF(B44="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Geografía urbana y rural</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E45" s="10">
+        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F45" s="10">
+        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G45" s="11">
+        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Enseñanza de la geografía 2 y residemcia pedagógica</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E46" s="10">
+        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F46" s="10">
+        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G46" s="11">
+        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Territorios 4: Africa y Oceania</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E47" s="10">
+        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F47" s="10">
+        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="11">
+        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Nuevas tecnologias</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E48" s="10">
+        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F48" s="10">
+        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G48" s="11">
+        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Lengua extranjera: Portugues</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E49" s="10">
+        <f>IF(B49="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F49" s="10">
+        <f>IF(C49="SI", "APROBADO", IF(B49="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G49" s="11">
+        <f>IF(C49="SI", "🟢 Aprobada", IF(B49="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Antropologia</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E50" s="10">
+        <f>IF(B50="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F50" s="10">
+        <f>IF(C50="SI", "APROBADO", IF(B50="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G50" s="11">
+        <f>IF(C50="SI", "🟢 Aprobada", IF(B50="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Esi</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E51" s="10">
+        <f>IF(B51="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F51" s="10">
+        <f>IF(C51="SI", "APROBADO", IF(B51="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G51" s="11">
+        <f>IF(C51="SI", "🟢 Aprobada", IF(B51="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A13:G13"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A27:G27"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A22:G22"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A38:G38"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A43:G43"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B23 B24 B25 B26 B27 B28 B29 B31 B32 B33 B34 B35 B36 B37 B39 B40 B41 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C23 C24 C25 C26 C27 C28 C29 C31 C32 C33 C34 C35 C36 C37 C39 C40 C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B18 B19 B20 B21 B22 B23 B24 B25 B26 B28 B29 B30 B31 B32 B33 B34 B35 B36 B38 B39 B40 B41 B42 B44 B45 B46 B47 B48 B49 B50 B51 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C18 C19 C20 C21 C22 C23 C24 C25 C26 C28 C29 C30 C31 C32 C33 C34 C35 C36 C38 C39 C40 C41 C42 C44 C45 C46 C47 C48 C49 C50 C51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
